--- a/product_selector_out/STM32U5 series.xlsx
+++ b/product_selector_out/STM32U5 series.xlsx
@@ -1968,7 +1968,7 @@
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u5a5aj.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="BM17" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u5a5aj.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4584,7 +4584,7 @@
       </c>
       <c r="BM22" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u5a5aj.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="BM24" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u5a5aj.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BM28" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u5a5aj.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="BM30" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u5f7vj.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -7527,7 +7527,7 @@
       </c>
       <c r="BM31" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u5f7vj.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -7854,7 +7854,7 @@
       </c>
       <c r="BM32" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u5f7vj.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -8181,7 +8181,7 @@
       </c>
       <c r="BM33" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u5g7vj.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -8508,7 +8508,7 @@
       </c>
       <c r="BM34" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u5f7vj.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -8835,7 +8835,7 @@
       </c>
       <c r="BM35" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u5g7vj.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -9162,7 +9162,7 @@
       </c>
       <c r="BM36" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u5g7vj.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -9489,7 +9489,7 @@
       </c>
       <c r="BM37" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u5g7vj.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -10470,7 +10470,7 @@
       </c>
       <c r="BM40" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u5a5aj.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -11451,7 +11451,7 @@
       </c>
       <c r="BM43" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u5a5aj.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -11778,7 +11778,7 @@
       </c>
       <c r="BM44" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u5a5aj.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -13086,7 +13086,7 @@
       </c>
       <c r="BM48" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u5a5aj.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -26086,9 +26086,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX12" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX12" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY12" s="9" t="inlineStr">
@@ -26413,9 +26413,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX13" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY13" s="9" t="inlineStr">
@@ -26515,9 +26515,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -26580,14 +26580,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R14" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S14" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T14" s="6" t="inlineStr">
@@ -26735,19 +26735,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW14" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY14" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ14" s="6" t="inlineStr">
@@ -26815,9 +26815,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -27067,9 +27067,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX15" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY15" s="9" t="inlineStr">
@@ -27394,9 +27394,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX16" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX16" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY16" s="9" t="inlineStr">
@@ -27496,9 +27496,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
@@ -27561,14 +27561,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R17" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S17" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T17" s="6" t="inlineStr">
@@ -27716,19 +27716,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW17" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX17" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY17" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ17" s="6" t="inlineStr">
@@ -27796,9 +27796,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -28048,9 +28048,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX18" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY18" s="9" t="inlineStr">
@@ -28375,9 +28375,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX19" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY19" s="9" t="inlineStr">
@@ -28702,9 +28702,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX20" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX20" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY20" s="9" t="inlineStr">
@@ -29029,9 +29029,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX21" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX21" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY21" s="9" t="inlineStr">
@@ -29131,9 +29131,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -29196,14 +29196,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R22" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S22" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T22" s="6" t="inlineStr">
@@ -29351,19 +29351,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW22" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX22" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY22" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ22" s="6" t="inlineStr">
@@ -29431,9 +29431,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -29683,9 +29683,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX23" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY23" s="9" t="inlineStr">
@@ -29785,9 +29785,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
@@ -29850,14 +29850,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R24" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S24" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T24" s="6" t="inlineStr">
@@ -30005,19 +30005,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW24" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX24" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY24" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ24" s="6" t="inlineStr">
@@ -30085,9 +30085,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -30337,9 +30337,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX25" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX25" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY25" s="9" t="inlineStr">
@@ -30664,9 +30664,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX26" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX26" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY26" s="9" t="inlineStr">
@@ -30991,9 +30991,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX27" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX27" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY27" s="9" t="inlineStr">
@@ -31093,9 +31093,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
@@ -31158,14 +31158,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R28" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S28" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T28" s="6" t="inlineStr">
@@ -31313,19 +31313,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW28" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX28" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY28" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ28" s="6" t="inlineStr">
@@ -31393,9 +31393,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -31645,9 +31645,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX29" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX29" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY29" s="9" t="inlineStr">
@@ -31747,9 +31747,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E30" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
@@ -31812,14 +31812,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R30" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S30" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T30" s="6" t="inlineStr">
@@ -31967,19 +31967,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW30" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX30" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY30" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ30" s="6" t="inlineStr">
@@ -32047,9 +32047,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM30" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM30" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -32074,9 +32074,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
@@ -32139,14 +32139,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R31" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S31" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T31" s="6" t="inlineStr">
@@ -32294,19 +32294,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW31" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX31" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY31" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ31" s="6" t="inlineStr">
@@ -32374,9 +32374,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM31" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM31" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -32401,9 +32401,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
@@ -32466,14 +32466,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R32" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S32" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S32" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T32" s="6" t="inlineStr">
@@ -32621,19 +32621,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW32" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX32" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY32" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW32" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX32" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY32" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ32" s="6" t="inlineStr">
@@ -32701,9 +32701,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM32" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM32" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -32728,9 +32728,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E33" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
@@ -32793,14 +32793,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R33" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S33" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S33" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T33" s="6" t="inlineStr">
@@ -32948,19 +32948,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW33" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX33" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY33" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW33" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX33" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY33" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ33" s="6" t="inlineStr">
@@ -33028,9 +33028,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM33" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM33" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -33055,9 +33055,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E34" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
@@ -33120,14 +33120,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R34" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S34" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S34" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T34" s="6" t="inlineStr">
@@ -33275,19 +33275,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW34" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX34" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY34" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW34" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX34" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY34" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ34" s="6" t="inlineStr">
@@ -33355,9 +33355,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM34" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM34" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -33382,9 +33382,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
@@ -33447,14 +33447,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R35" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S35" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S35" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T35" s="6" t="inlineStr">
@@ -33602,19 +33602,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW35" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX35" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY35" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW35" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX35" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY35" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ35" s="6" t="inlineStr">
@@ -33682,9 +33682,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM35" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM35" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -33709,9 +33709,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E36" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
@@ -33774,14 +33774,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R36" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S36" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S36" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T36" s="6" t="inlineStr">
@@ -33929,19 +33929,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW36" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX36" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY36" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW36" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX36" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY36" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ36" s="6" t="inlineStr">
@@ -34009,9 +34009,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM36" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM36" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -34036,9 +34036,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
@@ -34101,14 +34101,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R37" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S37" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S37" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T37" s="6" t="inlineStr">
@@ -34256,19 +34256,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW37" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX37" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY37" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW37" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX37" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY37" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ37" s="6" t="inlineStr">
@@ -34336,9 +34336,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM37" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM37" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -34588,9 +34588,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX38" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX38" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY38" s="9" t="inlineStr">
@@ -34915,9 +34915,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX39" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX39" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY39" s="9" t="inlineStr">
@@ -35017,9 +35017,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E40" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
@@ -35082,14 +35082,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R40" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S40" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S40" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T40" s="6" t="inlineStr">
@@ -35237,19 +35237,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW40" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX40" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY40" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW40" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX40" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY40" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ40" s="6" t="inlineStr">
@@ -35317,9 +35317,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM40" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM40" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -35569,9 +35569,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX41" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX41" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY41" s="9" t="inlineStr">
@@ -35896,9 +35896,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX42" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX42" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY42" s="9" t="inlineStr">
@@ -35998,9 +35998,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E43" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
@@ -36063,14 +36063,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R43" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S43" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S43" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T43" s="6" t="inlineStr">
@@ -36218,19 +36218,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW43" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX43" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY43" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW43" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX43" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY43" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ43" s="6" t="inlineStr">
@@ -36298,9 +36298,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM43" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM43" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -36325,9 +36325,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E44" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
@@ -36390,14 +36390,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R44" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S44" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S44" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T44" s="6" t="inlineStr">
@@ -36545,19 +36545,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW44" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX44" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY44" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW44" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX44" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY44" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ44" s="6" t="inlineStr">
@@ -36625,9 +36625,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM44" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM44" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -36877,9 +36877,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX45" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX45" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY45" s="9" t="inlineStr">
@@ -37204,9 +37204,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX46" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX46" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY46" s="9" t="inlineStr">
@@ -37531,9 +37531,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX47" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX47" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY47" s="9" t="inlineStr">
@@ -37633,9 +37633,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E48" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F48" s="6" t="inlineStr">
@@ -37698,14 +37698,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R48" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S48" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S48" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T48" s="6" t="inlineStr">
@@ -37853,19 +37853,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW48" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX48" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY48" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW48" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX48" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY48" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ48" s="6" t="inlineStr">
@@ -37933,9 +37933,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM48" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM48" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -38185,9 +38185,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX49" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX49" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY49" s="6" t="inlineStr">
@@ -38512,9 +38512,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX50" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX50" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY50" s="6" t="inlineStr">
@@ -38839,9 +38839,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX51" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX51" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY51" s="6" t="inlineStr">
@@ -39166,9 +39166,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX52" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX52" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY52" s="6" t="inlineStr">
@@ -39493,9 +39493,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX53" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX53" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY53" s="6" t="inlineStr">
@@ -39820,9 +39820,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX54" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX54" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY54" s="6" t="inlineStr">
@@ -40147,9 +40147,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX55" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX55" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY55" s="6" t="inlineStr">
@@ -40474,9 +40474,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX56" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX56" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY56" s="6" t="inlineStr">
@@ -40801,9 +40801,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX57" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX57" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY57" s="6" t="inlineStr">
@@ -41128,9 +41128,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX58" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX58" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY58" s="6" t="inlineStr">
@@ -41455,9 +41455,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX59" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX59" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY59" s="6" t="inlineStr">
@@ -41782,9 +41782,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX60" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX60" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY60" s="6" t="inlineStr">
@@ -42109,9 +42109,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX61" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX61" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY61" s="6" t="inlineStr">
@@ -42436,9 +42436,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX62" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX62" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY62" s="6" t="inlineStr">
@@ -42763,9 +42763,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX63" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX63" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY63" s="6" t="inlineStr">
@@ -43090,9 +43090,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX64" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX64" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY64" s="6" t="inlineStr">
@@ -43417,9 +43417,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX65" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX65" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY65" s="6" t="inlineStr">
@@ -43744,9 +43744,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX66" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX66" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY66" s="6" t="inlineStr">
@@ -44071,9 +44071,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX67" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX67" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY67" s="6" t="inlineStr">
@@ -44398,9 +44398,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX68" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX68" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY68" s="6" t="inlineStr">
@@ -44725,9 +44725,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX69" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX69" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY69" s="6" t="inlineStr">
@@ -45052,9 +45052,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX70" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX70" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY70" s="6" t="inlineStr">
@@ -45379,9 +45379,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX71" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX71" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY71" s="6" t="inlineStr">
@@ -45706,9 +45706,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX72" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX72" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY72" s="6" t="inlineStr">
@@ -46033,9 +46033,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX73" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX73" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY73" s="6" t="inlineStr">
@@ -46360,9 +46360,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX74" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX74" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY74" s="6" t="inlineStr">
@@ -46687,9 +46687,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX75" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX75" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY75" s="6" t="inlineStr">
@@ -47014,9 +47014,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX76" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX76" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY76" s="6" t="inlineStr">
@@ -47341,9 +47341,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX77" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX77" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY77" s="6" t="inlineStr">
@@ -47668,9 +47668,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX78" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX78" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY78" s="6" t="inlineStr">
@@ -47995,9 +47995,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX79" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX79" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY79" s="6" t="inlineStr">
@@ -48322,9 +48322,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX80" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX80" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY80" s="6" t="inlineStr">
@@ -48649,9 +48649,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX81" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX81" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY81" s="6" t="inlineStr">
@@ -48976,9 +48976,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX82" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX82" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY82" s="6" t="inlineStr">
@@ -49303,9 +49303,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX83" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX83" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY83" s="6" t="inlineStr">
@@ -49630,9 +49630,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX84" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX84" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY84" s="6" t="inlineStr">
@@ -49957,9 +49957,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX85" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX85" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY85" s="6" t="inlineStr">
@@ -50053,7 +50053,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D260"/>
+  <dimension ref="A1:D249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -50146,7 +50146,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -50158,7 +50158,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -50168,19 +50168,19 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Table 72. Typical dynamic current consumption of peripherals</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STM32U5G7VJ</t>
+          <t>STM32U5F7VJ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -50190,7 +50190,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 72. Typical dynamic current consumption of peripherals</t>
         </is>
       </c>
     </row>
@@ -50202,7 +50202,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -50224,7 +50224,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -50234,7 +50234,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 20. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
@@ -50246,7 +50246,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -50256,19 +50256,19 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Table 73. Typical dynamic current consumption of peripherals</t>
+          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STM32U5A5VJ</t>
+          <t>STM32U5G7VJ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -50278,19 +50278,19 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STM32U5A5VJ</t>
+          <t>STM32U5G7VJ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -50300,19 +50300,19 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 73. Typical dynamic current consumption of peripherals</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STM32U5A5VJ</t>
+          <t>STM32U595ZJ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -50322,19 +50322,19 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STM32U5A5VJ</t>
+          <t>STM32U595ZJ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -50344,7 +50344,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Table 65. Typical dynamic current consumption of peripherals</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
@@ -50356,7 +50356,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -50366,7 +50366,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -50378,7 +50378,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -50388,7 +50388,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
@@ -50400,7 +50400,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -50410,19 +50410,19 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 64. Typical dynamic current consumption of peripherals</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>STM32U595ZJ</t>
+          <t>STM32U595QJ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -50432,7 +50432,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Table 64. Typical dynamic current consumption of peripherals</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
@@ -50444,7 +50444,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -50466,7 +50466,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -50476,7 +50476,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -50488,7 +50488,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -50498,7 +50498,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
@@ -50527,7 +50527,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>STM32U5A5QJ</t>
+          <t>STM32U595QI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -50542,14 +50542,14 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>STM32U5A5QJ</t>
+          <t>STM32U595QI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -50564,14 +50564,14 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>STM32U5A5QJ</t>
+          <t>STM32U595QI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -50586,19 +50586,19 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>STM32U5A5QJ</t>
+          <t>STM32U595QI</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -50608,7 +50608,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Table 65. Typical dynamic current consumption of peripherals</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
@@ -50620,7 +50620,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -50630,19 +50630,19 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 64. Typical dynamic current consumption of peripherals</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>STM32U595QI</t>
+          <t>STM32U595VI</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -50659,12 +50659,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>STM32U595QI</t>
+          <t>STM32U595VI</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -50674,19 +50674,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STM32U595QI</t>
+          <t>STM32U595VI</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -50696,7 +50696,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Table 64. Typical dynamic current consumption of peripherals</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -50708,7 +50708,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -50718,7 +50718,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
@@ -50730,7 +50730,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -50740,19 +50740,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 64. Typical dynamic current consumption of peripherals</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STM32U595VI</t>
+          <t>STM32U595RI</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -50762,19 +50762,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STM32U595VI</t>
+          <t>STM32U595RI</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -50784,7 +50784,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Table 64. Typical dynamic current consumption of peripherals</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
@@ -50796,7 +50796,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -50806,7 +50806,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -50818,7 +50818,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -50828,7 +50828,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
@@ -50840,7 +50840,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -50850,19 +50850,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 64. Typical dynamic current consumption of peripherals</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STM32U595RI</t>
+          <t>STM32U595VJ</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -50872,7 +50872,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Table 64. Typical dynamic current consumption of peripherals</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
@@ -50884,7 +50884,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -50906,7 +50906,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -50916,7 +50916,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -50928,7 +50928,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -50938,7 +50938,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
@@ -50967,7 +50967,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>STM32U5A5ZJ</t>
+          <t>STM32U595AI</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -50982,14 +50982,14 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>STM32U5A5ZJ</t>
+          <t>STM32U595AI</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -51004,14 +51004,14 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STM32U5A5ZJ</t>
+          <t>STM32U595AI</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -51026,19 +51026,19 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>STM32U5A5ZJ</t>
+          <t>STM32U595AI</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -51048,7 +51048,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Table 65. Typical dynamic current consumption of peripherals</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
@@ -51060,7 +51060,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -51070,19 +51070,19 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 64. Typical dynamic current consumption of peripherals</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>STM32U595AI</t>
+          <t>STM32U595ZI</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -51099,12 +51099,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>STM32U595AI</t>
+          <t>STM32U595ZI</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -51114,19 +51114,19 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STM32U595AI</t>
+          <t>STM32U595ZI</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -51136,19 +51136,19 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Table 64. Typical dynamic current consumption of peripherals</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STM32U5A5QI</t>
+          <t>STM32U595ZI</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -51158,19 +51158,19 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>STM32U5A5QI</t>
+          <t>STM32U595ZI</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -51180,19 +51180,19 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 64. Typical dynamic current consumption of peripherals</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>STM32U5A5QI</t>
+          <t>STM32U595RJ</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -51202,19 +51202,19 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>STM32U5A5QI</t>
+          <t>STM32U595RJ</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -51224,19 +51224,19 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Table 65. Typical dynamic current consumption of peripherals</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>STM32U595ZI</t>
+          <t>STM32U595RJ</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -51246,19 +51246,19 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>STM32U595ZI</t>
+          <t>STM32U595RJ</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -51268,19 +51268,19 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>STM32U595ZI</t>
+          <t>STM32U595RJ</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -51290,19 +51290,19 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 64. Typical dynamic current consumption of peripherals</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>STM32U595ZI</t>
+          <t>STM32U5A5AJ</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -51312,19 +51312,19 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Table 64. Typical dynamic current consumption of peripherals</t>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>STM32U595RJ</t>
+          <t>STM32U5A5AJ</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -51334,19 +51334,19 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>STM32U595RJ</t>
+          <t>STM32U5A5AJ</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -51356,19 +51356,19 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STM32U595RJ</t>
+          <t>STM32U5A5AJ</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -51378,14 +51378,14 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>STM32U595RJ</t>
+          <t>STM32U5A5AJ</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -51400,14 +51400,14 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Table 64. Typical dynamic current consumption of peripherals</t>
+          <t>Table 65. Typical dynamic current consumption of peripherals</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>STM32U5A5AJ</t>
+          <t>STM32U595AJ</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -51422,14 +51422,14 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STM32U5A5AJ</t>
+          <t>STM32U595AJ</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -51444,14 +51444,14 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>STM32U5A5AJ</t>
+          <t>STM32U595AJ</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -51466,19 +51466,19 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>STM32U5A5AJ</t>
+          <t>STM32U595AJ</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -51488,19 +51488,19 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Table 65. Typical dynamic current consumption of peripherals</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>STM32U5A5RJ</t>
+          <t>STM32U595AJ</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -51510,19 +51510,19 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 64. Typical dynamic current consumption of peripherals</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STM32U5A5RJ</t>
+          <t>STM32U599NI</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -51532,19 +51532,19 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>STM32U5A5RJ</t>
+          <t>STM32U599NI</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -51554,19 +51554,19 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STM32U5A5RJ</t>
+          <t>STM32U599NI</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -51576,19 +51576,19 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Table 65. Typical dynamic current consumption of peripherals</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>STM32U595AJ</t>
+          <t>STM32U599NI</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -51598,19 +51598,19 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>STM32U595AJ</t>
+          <t>STM32U599NI</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -51620,19 +51620,19 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 64. Typical dynamic current consumption of peripherals</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>STM32U595AJ</t>
+          <t>STM32U599VJ</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -51642,19 +51642,19 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>STM32U595AJ</t>
+          <t>STM32U599VJ</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -51664,19 +51664,19 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Table 64. Typical dynamic current consumption of peripherals</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>STM32U5F9VJ</t>
+          <t>STM32U599VJ</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -51686,19 +51686,19 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>STM32U5F9VJ</t>
+          <t>STM32U599VJ</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -51708,19 +51708,19 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>STM32U5F9VJ</t>
+          <t>STM32U599VJ</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -51730,19 +51730,19 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 64. Typical dynamic current consumption of peripherals</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>STM32U5F9VJ</t>
+          <t>STM32U599ZI</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -51752,19 +51752,19 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Table 72. Typical dynamic current consumption of peripherals</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>STM32U5F9NJ</t>
+          <t>STM32U599ZI</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -51774,19 +51774,19 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>STM32U5F9NJ</t>
+          <t>STM32U599ZI</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -51796,19 +51796,19 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>STM32U5F9NJ</t>
+          <t>STM32U599ZI</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -51818,14 +51818,14 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>STM32U5F9NJ</t>
+          <t>STM32U599ZI</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -51840,14 +51840,14 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Table 72. Typical dynamic current consumption of peripherals</t>
+          <t>Table 64. Typical dynamic current consumption of peripherals</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>STM32U5F9BJ</t>
+          <t>STM32U599VI</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -51862,14 +51862,14 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>STM32U5F9BJ</t>
+          <t>STM32U599VI</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -51884,14 +51884,14 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>STM32U5F9BJ</t>
+          <t>STM32U599VI</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -51906,19 +51906,19 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>STM32U5F9BJ</t>
+          <t>STM32U599VI</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -51928,19 +51928,19 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Table 72. Typical dynamic current consumption of peripherals</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>STM32U5G9BJ</t>
+          <t>STM32U599VI</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -51950,19 +51950,19 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 64. Typical dynamic current consumption of peripherals</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>STM32U5G9BJ</t>
+          <t>STM32U599NJ</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -51972,19 +51972,19 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>STM32U5G9BJ</t>
+          <t>STM32U599NJ</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -51994,19 +51994,19 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>STM32U5G9BJ</t>
+          <t>STM32U599NJ</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -52016,19 +52016,19 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Table 73. Typical dynamic current consumption of peripherals</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>STM32U5F9ZJ</t>
+          <t>STM32U599NJ</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -52038,19 +52038,19 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>STM32U5F9ZJ</t>
+          <t>STM32U599NJ</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -52060,19 +52060,19 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 64. Typical dynamic current consumption of peripherals</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>STM32U5F9ZJ</t>
+          <t>STM32U599BJ</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -52082,19 +52082,19 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>STM32U5F9ZJ</t>
+          <t>STM32U599BJ</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -52104,19 +52104,19 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Table 72. Typical dynamic current consumption of peripherals</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>STM32U5G9ZJ</t>
+          <t>STM32U599BJ</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -52126,19 +52126,19 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>STM32U5G9ZJ</t>
+          <t>STM32U599BJ</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -52148,19 +52148,19 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>STM32U5G9ZJ</t>
+          <t>STM32U599BJ</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -52170,19 +52170,19 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 64. Typical dynamic current consumption of peripherals</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>STM32U5G9ZJ</t>
+          <t>STM32U599ZJ</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -52192,19 +52192,19 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Table 73. Typical dynamic current consumption of peripherals</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>STM32U5G9VJ</t>
+          <t>STM32U599ZJ</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -52214,19 +52214,19 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>STM32U5G9VJ</t>
+          <t>STM32U599ZJ</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -52236,19 +52236,19 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>STM32U5G9VJ</t>
+          <t>STM32U599ZJ</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -52258,14 +52258,14 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>STM32U5G9VJ</t>
+          <t>STM32U599ZJ</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -52280,14 +52280,14 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Table 73. Typical dynamic current consumption of peripherals</t>
+          <t>Table 64. Typical dynamic current consumption of peripherals</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>STM32U5G9NJ</t>
+          <t>STM32U575RG</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -52302,14 +52302,14 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>STM32U5G9NJ</t>
+          <t>STM32U575RG</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -52324,14 +52324,14 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>STM32U5G9NJ</t>
+          <t>STM32U575RG</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -52346,19 +52346,19 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>STM32U5G9NJ</t>
+          <t>STM32U575RG</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -52368,14 +52368,14 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Table 73. Typical dynamic current consumption of peripherals</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>STM32U599NI</t>
+          <t>STM32U585VI</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -52390,14 +52390,14 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>STM32U599NI</t>
+          <t>STM32U585VI</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -52412,14 +52412,14 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>STM32U599NI</t>
+          <t>STM32U585VI</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -52434,19 +52434,19 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>STM32U599NI</t>
+          <t>STM32U585VI</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -52456,14 +52456,14 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Table 64. Typical dynamic current consumption of peripherals</t>
+          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>STM32U599VJ</t>
+          <t>STM32U575RI</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -52485,7 +52485,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>STM32U599VJ</t>
+          <t>STM32U575RI</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -52507,7 +52507,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>STM32U599VJ</t>
+          <t>STM32U575RI</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -52522,19 +52522,19 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>STM32U599VJ</t>
+          <t>STM32U575RI</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -52544,14 +52544,14 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Table 64. Typical dynamic current consumption of peripherals</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>STM32U5A9VJ</t>
+          <t>STM32U575VG</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -52566,14 +52566,14 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>STM32U5A9VJ</t>
+          <t>STM32U575VG</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -52588,14 +52588,14 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>STM32U5A9VJ</t>
+          <t>STM32U575VG</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -52610,19 +52610,19 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>STM32U5A9VJ</t>
+          <t>STM32U575VG</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -52632,14 +52632,14 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Table 65. Typical dynamic current consumption of peripherals</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>STM32U599ZI</t>
+          <t>STM32U575AG</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -52661,7 +52661,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>STM32U599ZI</t>
+          <t>STM32U575AG</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -52683,7 +52683,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>STM32U599ZI</t>
+          <t>STM32U575AG</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -52698,19 +52698,19 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>STM32U599ZI</t>
+          <t>STM32U575AG</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -52720,14 +52720,14 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Table 64. Typical dynamic current consumption of peripherals</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>STM32U599VI</t>
+          <t>STM32U575VI</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -52749,7 +52749,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>STM32U599VI</t>
+          <t>STM32U575VI</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -52771,7 +52771,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>STM32U599VI</t>
+          <t>STM32U575VI</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -52786,19 +52786,19 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>STM32U599VI</t>
+          <t>STM32U575VI</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -52808,14 +52808,14 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Table 64. Typical dynamic current consumption of peripherals</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>STM32U5A9NJ</t>
+          <t>STM32U575ZG</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -52830,14 +52830,14 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>STM32U5A9NJ</t>
+          <t>STM32U575ZG</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -52852,14 +52852,14 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>STM32U5A9NJ</t>
+          <t>STM32U575ZG</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -52874,19 +52874,19 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>STM32U5A9NJ</t>
+          <t>STM32U575ZG</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -52896,14 +52896,14 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Table 65. Typical dynamic current consumption of peripherals</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>STM32U5A9BJ</t>
+          <t>STM32U575AI</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -52918,14 +52918,14 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>STM32U5A9BJ</t>
+          <t>STM32U575AI</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -52940,14 +52940,14 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>STM32U5A9BJ</t>
+          <t>STM32U575AI</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -52962,19 +52962,19 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>STM32U5A9BJ</t>
+          <t>STM32U575AI</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -52984,14 +52984,14 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Table 65. Typical dynamic current consumption of peripherals</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>STM32U599NJ</t>
+          <t>STM32U575CG</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -53013,7 +53013,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>STM32U599NJ</t>
+          <t>STM32U575CG</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -53035,7 +53035,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>STM32U599NJ</t>
+          <t>STM32U575CG</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -53050,19 +53050,19 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>STM32U599NJ</t>
+          <t>STM32U575CG</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -53072,14 +53072,14 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Table 64. Typical dynamic current consumption of peripherals</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>STM32U599BJ</t>
+          <t>STM32U575ZI</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -53101,7 +53101,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>STM32U599BJ</t>
+          <t>STM32U575ZI</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -53123,7 +53123,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>STM32U599BJ</t>
+          <t>STM32U575ZI</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -53138,19 +53138,19 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>STM32U599BJ</t>
+          <t>STM32U575ZI</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -53160,14 +53160,14 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Table 64. Typical dynamic current consumption of peripherals</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>STM32U599ZJ</t>
+          <t>STM32U575CI</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -53189,7 +53189,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>STM32U599ZJ</t>
+          <t>STM32U575CI</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -53211,7 +53211,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>STM32U599ZJ</t>
+          <t>STM32U575CI</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -53226,19 +53226,19 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>STM32U599ZJ</t>
+          <t>STM32U575CI</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -53248,14 +53248,14 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Table 64. Typical dynamic current consumption of peripherals</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>STM32U5A9ZJ</t>
+          <t>STM32U585AI</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -53277,7 +53277,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>STM32U5A9ZJ</t>
+          <t>STM32U585AI</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -53299,7 +53299,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>STM32U5A9ZJ</t>
+          <t>STM32U585AI</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -53314,19 +53314,19 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>STM32U5A9ZJ</t>
+          <t>STM32U585AI</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -53336,14 +53336,14 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Table 65. Typical dynamic current consumption of peripherals</t>
+          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>STM32U575RG</t>
+          <t>STM32U575OG</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -53365,7 +53365,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>STM32U575RG</t>
+          <t>STM32U575OG</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -53387,7 +53387,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>STM32U575RG</t>
+          <t>STM32U575OG</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -53402,19 +53402,19 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>STM32U585VI</t>
+          <t>STM32U575OG</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -53424,19 +53424,19 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>STM32U585VI</t>
+          <t>STM32U585CI</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -53453,12 +53453,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>STM32U585VI</t>
+          <t>STM32U585CI</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -53468,19 +53468,19 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>STM32U575RI</t>
+          <t>STM32U585CI</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -53490,19 +53490,19 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>STM32U575RI</t>
+          <t>STM32U585CI</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -53512,19 +53512,19 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>STM32U575RI</t>
+          <t>STM32U585ZI</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -53534,19 +53534,19 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>STM32U575VG</t>
+          <t>STM32U585ZI</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -53556,19 +53556,19 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>STM32U575VG</t>
+          <t>STM32U585ZI</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -53578,19 +53578,19 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>STM32U575VG</t>
+          <t>STM32U585ZI</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -53600,14 +53600,14 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>STM32U575AG</t>
+          <t>STM32U575OI</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -53629,7 +53629,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>STM32U575AG</t>
+          <t>STM32U575OI</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -53651,7 +53651,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>STM32U575AG</t>
+          <t>STM32U575OI</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -53666,19 +53666,19 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>STM32U575VI</t>
+          <t>STM32U575OI</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -53688,19 +53688,19 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>STM32U575VI</t>
+          <t>STM32U585OI</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -53710,19 +53710,19 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>STM32U575VI</t>
+          <t>STM32U585OI</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -53732,19 +53732,19 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>STM32U575ZG</t>
+          <t>STM32U585OI</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -53754,19 +53754,19 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>STM32U575ZG</t>
+          <t>STM32U585OI</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -53776,19 +53776,19 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>STM32U575ZG</t>
+          <t>STM32U575QG</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -53798,19 +53798,19 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>STM32U575AI</t>
+          <t>STM32U575QG</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -53827,12 +53827,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>STM32U575AI</t>
+          <t>STM32U575QG</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -53842,19 +53842,19 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>STM32U575AI</t>
+          <t>STM32U575QG</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -53864,14 +53864,14 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>STM32U575CG</t>
+          <t>STM32U585QI</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -53886,14 +53886,14 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>STM32U575CG</t>
+          <t>STM32U585QI</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -53908,14 +53908,14 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>STM32U575CG</t>
+          <t>STM32U585QI</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -53930,19 +53930,19 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>STM32U575ZI</t>
+          <t>STM32U585QI</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -53952,19 +53952,19 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>STM32U575ZI</t>
+          <t>STM32U585RI</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -53974,19 +53974,19 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>STM32U575ZI</t>
+          <t>STM32U585RI</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -53996,19 +53996,19 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>STM32U575CI</t>
+          <t>STM32U585RI</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -54018,19 +54018,19 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>STM32U575CI</t>
+          <t>STM32U585RI</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -54040,19 +54040,19 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>STM32U575CI</t>
+          <t>STM32U575QI</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -54062,19 +54062,19 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>STM32U585AI</t>
+          <t>STM32U575QI</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -54084,19 +54084,19 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>STM32U585AI</t>
+          <t>STM32U575QI</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -54106,19 +54106,19 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>STM32U585AI</t>
+          <t>STM32U575QI</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -54128,14 +54128,14 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>STM32U575OG</t>
+          <t>STM32U535CE</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -54157,7 +54157,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>STM32U575OG</t>
+          <t>STM32U535CE</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -54179,7 +54179,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>STM32U575OG</t>
+          <t>STM32U535CE</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -54194,19 +54194,19 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>STM32U585CI</t>
+          <t>STM32U535CE</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -54216,19 +54216,19 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>STM32U585CI</t>
+          <t>STM32U545VE</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -54245,12 +54245,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>STM32U585CI</t>
+          <t>STM32U545VE</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -54260,19 +54260,19 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>STM32U585ZI</t>
+          <t>STM32U545VE</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -54282,19 +54282,19 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>STM32U585ZI</t>
+          <t>STM32U545VE</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -54304,19 +54304,19 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>STM32U585ZI</t>
+          <t>STM32U535VE</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -54326,19 +54326,19 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>STM32U575OI</t>
+          <t>STM32U535VE</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -54355,12 +54355,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>STM32U575OI</t>
+          <t>STM32U535VE</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -54370,19 +54370,19 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>STM32U575OI</t>
+          <t>STM32U535VE</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -54392,14 +54392,14 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>STM32U585OI</t>
+          <t>STM32U545RE</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -54421,7 +54421,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>STM32U585OI</t>
+          <t>STM32U545RE</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -54443,7 +54443,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>STM32U585OI</t>
+          <t>STM32U545RE</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -54458,19 +54458,19 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>STM32U575QG</t>
+          <t>STM32U545RE</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -54480,19 +54480,19 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>STM32U575QG</t>
+          <t>STM32U535RE</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -54509,12 +54509,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>STM32U575QG</t>
+          <t>STM32U535RE</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -54524,19 +54524,19 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>STM32U585QI</t>
+          <t>STM32U535RE</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -54546,19 +54546,19 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>STM32U585QI</t>
+          <t>STM32U535RE</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -54568,19 +54568,19 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>STM32U585QI</t>
+          <t>STM32U545CE</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -54590,19 +54590,19 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>STM32U585RI</t>
+          <t>STM32U545CE</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -54619,12 +54619,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>STM32U585RI</t>
+          <t>STM32U545CE</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -54634,19 +54634,19 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>STM32U585RI</t>
+          <t>STM32U545CE</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -54656,14 +54656,14 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>STM32U575QI</t>
+          <t>STM32U535RB</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -54685,7 +54685,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>STM32U575QI</t>
+          <t>STM32U535RB</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -54707,7 +54707,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>STM32U575QI</t>
+          <t>STM32U535RB</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -54722,19 +54722,19 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>STM32U535CE</t>
+          <t>STM32U535RB</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -54744,19 +54744,19 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>STM32U535CE</t>
+          <t>STM32U535CC</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -54773,12 +54773,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>STM32U535CE</t>
+          <t>STM32U535CC</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -54788,19 +54788,19 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>STM32U545VE</t>
+          <t>STM32U535CC</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -54810,19 +54810,19 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>STM32U545VE</t>
+          <t>STM32U535CC</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -54832,19 +54832,19 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>STM32U545VE</t>
+          <t>STM32U535CB</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -54854,19 +54854,19 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>STM32U535VE</t>
+          <t>STM32U535CB</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -54883,12 +54883,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>STM32U535VE</t>
+          <t>STM32U535CB</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -54898,19 +54898,19 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>STM32U535VE</t>
+          <t>STM32U535CB</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -54920,14 +54920,14 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>STM32U545RE</t>
+          <t>STM32U545JE</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -54949,7 +54949,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>STM32U545RE</t>
+          <t>STM32U545JE</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -54971,7 +54971,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>STM32U545RE</t>
+          <t>STM32U545JE</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -54986,19 +54986,19 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>STM32U535RE</t>
+          <t>STM32U545JE</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -55008,19 +55008,19 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>STM32U535RE</t>
+          <t>STM32U535RC</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -55037,12 +55037,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>STM32U535RE</t>
+          <t>STM32U535RC</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -55052,19 +55052,19 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>STM32U545CE</t>
+          <t>STM32U535RC</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -55074,19 +55074,19 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>STM32U545CE</t>
+          <t>STM32U535RC</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -55096,19 +55096,19 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>STM32U545CE</t>
+          <t>STM32U535JE</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -55118,19 +55118,19 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>STM32U535RB</t>
+          <t>STM32U535JE</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -55147,12 +55147,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>STM32U535RB</t>
+          <t>STM32U535JE</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -55162,19 +55162,19 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>STM32U535RB</t>
+          <t>STM32U535JE</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -55184,14 +55184,14 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>STM32U535CC</t>
+          <t>STM32U535VC</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -55213,7 +55213,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>STM32U535CC</t>
+          <t>STM32U535VC</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -55235,7 +55235,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>STM32U535CC</t>
+          <t>STM32U535VC</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -55250,19 +55250,19 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>STM32U535CB</t>
+          <t>STM32U535VC</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -55272,19 +55272,19 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>STM32U535CB</t>
+          <t>STM32U535NE</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -55301,12 +55301,12 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>STM32U535CB</t>
+          <t>STM32U535NE</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -55316,19 +55316,19 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>STM32U545JE</t>
+          <t>STM32U535NE</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -55338,19 +55338,19 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>STM32U545JE</t>
+          <t>STM32U535NE</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -55360,19 +55360,19 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>STM32U545JE</t>
+          <t>STM32U545NE</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -55382,19 +55382,19 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>STM32U535RC</t>
+          <t>STM32U545NE</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -55404,19 +55404,19 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>STM32U535RC</t>
+          <t>STM32U545NE</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -55426,19 +55426,19 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>STM32U535RC</t>
+          <t>STM32U545NE</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -55448,14 +55448,14 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>STM32U535JE</t>
+          <t>STM32U535NC</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -55477,7 +55477,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>STM32U535JE</t>
+          <t>STM32U535NC</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -55499,7 +55499,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>STM32U535JE</t>
+          <t>STM32U535NC</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -55514,19 +55514,19 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>STM32U535VC</t>
+          <t>STM32U535NC</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -55536,249 +55536,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>STM32U535VC</t>
-        </is>
-      </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr">
-        <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>STM32U535VC</t>
-        </is>
-      </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr">
-        <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>STM32U535NE</t>
-        </is>
-      </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C252" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D252" t="inlineStr">
-        <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="inlineStr">
-        <is>
-          <t>STM32U535NE</t>
-        </is>
-      </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C253" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr">
-        <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t>STM32U535NE</t>
-        </is>
-      </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C254" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D254" t="inlineStr">
-        <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="inlineStr">
-        <is>
-          <t>STM32U545NE</t>
-        </is>
-      </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C255" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr">
-        <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="inlineStr">
-        <is>
-          <t>STM32U545NE</t>
-        </is>
-      </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C256" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D256" t="inlineStr">
-        <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="inlineStr">
-        <is>
-          <t>STM32U545NE</t>
-        </is>
-      </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C257" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D257" t="inlineStr">
-        <is>
-          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="inlineStr">
-        <is>
-          <t>STM32U535NC</t>
-        </is>
-      </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D258" t="inlineStr">
-        <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="inlineStr">
-        <is>
-          <t>STM32U535NC</t>
-        </is>
-      </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C259" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D259" t="inlineStr">
-        <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="inlineStr">
-        <is>
-          <t>STM32U535NC</t>
-        </is>
-      </c>
-      <c r="B260" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C260" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D260" t="inlineStr">
-        <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>

--- a/product_selector_out/STM32U5 series.xlsx
+++ b/product_selector_out/STM32U5 series.xlsx
@@ -1968,7 +1968,7 @@
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32u5a5aj.pdf</t>
         </is>
       </c>
     </row>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="BM17" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32u5a5aj.pdf</t>
         </is>
       </c>
     </row>
@@ -4584,7 +4584,7 @@
       </c>
       <c r="BM22" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32u5a5aj.pdf</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="BM24" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32u5a5aj.pdf</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BM28" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32u5a5aj.pdf</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="BM30" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32u5f7vj.pdf</t>
         </is>
       </c>
     </row>
@@ -7527,7 +7527,7 @@
       </c>
       <c r="BM31" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32u5f7vj.pdf</t>
         </is>
       </c>
     </row>
@@ -7854,7 +7854,7 @@
       </c>
       <c r="BM32" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32u5f7vj.pdf</t>
         </is>
       </c>
     </row>
@@ -8181,7 +8181,7 @@
       </c>
       <c r="BM33" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32u5g7vj.pdf</t>
         </is>
       </c>
     </row>
@@ -8508,7 +8508,7 @@
       </c>
       <c r="BM34" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32u5f7vj.pdf</t>
         </is>
       </c>
     </row>
@@ -8835,7 +8835,7 @@
       </c>
       <c r="BM35" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32u5g7vj.pdf</t>
         </is>
       </c>
     </row>
@@ -9162,7 +9162,7 @@
       </c>
       <c r="BM36" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32u5g7vj.pdf</t>
         </is>
       </c>
     </row>
@@ -9489,7 +9489,7 @@
       </c>
       <c r="BM37" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32u5g7vj.pdf</t>
         </is>
       </c>
     </row>
@@ -10470,7 +10470,7 @@
       </c>
       <c r="BM40" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32u5a5aj.pdf</t>
         </is>
       </c>
     </row>
@@ -11451,7 +11451,7 @@
       </c>
       <c r="BM43" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32u5a5aj.pdf</t>
         </is>
       </c>
     </row>
@@ -11778,7 +11778,7 @@
       </c>
       <c r="BM44" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32u5a5aj.pdf</t>
         </is>
       </c>
     </row>
@@ -13086,7 +13086,7 @@
       </c>
       <c r="BM48" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32u5a5aj.pdf</t>
         </is>
       </c>
     </row>
@@ -26515,9 +26515,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -26580,14 +26580,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R14" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S14" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T14" s="6" t="inlineStr">
@@ -26735,19 +26735,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW14" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX14" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY14" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AZ14" s="6" t="inlineStr">
@@ -26815,9 +26815,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -27496,9 +27496,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
@@ -27561,14 +27561,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R17" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S17" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T17" s="6" t="inlineStr">
@@ -27716,19 +27716,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW17" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX17" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY17" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AZ17" s="6" t="inlineStr">
@@ -27796,9 +27796,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -29131,9 +29131,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -29196,14 +29196,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R22" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S22" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T22" s="6" t="inlineStr">
@@ -29351,19 +29351,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW22" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX22" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY22" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AZ22" s="6" t="inlineStr">
@@ -29431,9 +29431,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -29785,9 +29785,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
@@ -29850,14 +29850,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R24" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S24" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T24" s="6" t="inlineStr">
@@ -30005,19 +30005,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW24" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX24" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY24" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AZ24" s="6" t="inlineStr">
@@ -30085,9 +30085,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -31093,9 +31093,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
@@ -31158,14 +31158,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R28" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S28" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T28" s="6" t="inlineStr">
@@ -31313,19 +31313,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW28" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX28" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY28" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AZ28" s="6" t="inlineStr">
@@ -31393,9 +31393,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM28" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -31747,9 +31747,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E30" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
@@ -31812,14 +31812,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S30" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R30" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S30" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T30" s="6" t="inlineStr">
@@ -31967,19 +31967,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW30" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX30" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY30" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW30" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX30" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY30" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AZ30" s="6" t="inlineStr">
@@ -32047,9 +32047,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM30" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -32074,9 +32074,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E31" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
@@ -32139,14 +32139,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S31" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R31" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S31" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T31" s="6" t="inlineStr">
@@ -32294,19 +32294,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW31" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX31" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY31" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW31" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX31" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY31" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AZ31" s="6" t="inlineStr">
@@ -32374,9 +32374,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM31" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -32401,9 +32401,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E32" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
@@ -32466,14 +32466,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S32" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R32" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S32" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T32" s="6" t="inlineStr">
@@ -32621,19 +32621,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW32" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX32" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY32" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW32" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX32" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY32" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AZ32" s="6" t="inlineStr">
@@ -32701,9 +32701,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM32" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM32" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -32728,9 +32728,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E33" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
@@ -32793,14 +32793,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S33" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R33" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S33" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T33" s="6" t="inlineStr">
@@ -32948,19 +32948,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW33" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX33" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY33" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW33" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX33" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY33" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AZ33" s="6" t="inlineStr">
@@ -33028,9 +33028,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM33" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM33" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -33055,9 +33055,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E34" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
@@ -33120,14 +33120,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R34" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S34" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R34" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S34" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T34" s="6" t="inlineStr">
@@ -33275,19 +33275,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW34" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX34" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY34" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW34" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX34" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY34" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AZ34" s="6" t="inlineStr">
@@ -33355,9 +33355,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM34" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM34" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -33382,9 +33382,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E35" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
@@ -33447,14 +33447,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S35" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R35" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S35" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T35" s="6" t="inlineStr">
@@ -33602,19 +33602,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW35" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX35" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY35" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW35" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX35" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY35" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AZ35" s="6" t="inlineStr">
@@ -33682,9 +33682,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM35" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM35" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -33709,9 +33709,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E36" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
@@ -33774,14 +33774,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S36" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R36" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S36" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T36" s="6" t="inlineStr">
@@ -33929,19 +33929,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW36" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX36" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY36" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW36" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX36" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY36" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AZ36" s="6" t="inlineStr">
@@ -34009,9 +34009,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM36" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM36" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -34036,9 +34036,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E37" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
@@ -34101,14 +34101,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S37" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R37" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S37" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T37" s="6" t="inlineStr">
@@ -34256,19 +34256,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW37" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX37" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY37" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW37" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX37" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY37" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AZ37" s="6" t="inlineStr">
@@ -34336,9 +34336,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM37" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM37" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -35017,9 +35017,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E40" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
@@ -35082,14 +35082,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S40" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R40" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S40" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T40" s="6" t="inlineStr">
@@ -35237,19 +35237,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW40" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX40" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY40" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW40" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX40" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY40" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AZ40" s="6" t="inlineStr">
@@ -35317,9 +35317,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM40" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM40" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -35998,9 +35998,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E43" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
@@ -36063,14 +36063,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S43" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R43" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S43" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T43" s="6" t="inlineStr">
@@ -36218,19 +36218,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW43" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX43" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY43" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW43" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX43" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY43" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AZ43" s="6" t="inlineStr">
@@ -36298,9 +36298,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM43" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM43" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -36325,9 +36325,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E44" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
@@ -36390,14 +36390,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S44" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R44" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S44" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T44" s="6" t="inlineStr">
@@ -36545,19 +36545,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW44" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX44" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY44" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW44" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX44" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY44" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AZ44" s="6" t="inlineStr">
@@ -36625,9 +36625,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM44" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM44" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -37633,9 +37633,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E48" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F48" s="6" t="inlineStr">
@@ -37698,14 +37698,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S48" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R48" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S48" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T48" s="6" t="inlineStr">
@@ -37853,19 +37853,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW48" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX48" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY48" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW48" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX48" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY48" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AZ48" s="6" t="inlineStr">
@@ -37933,9 +37933,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM48" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM48" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -50053,7 +50053,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D249"/>
+  <dimension ref="A1:D334"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -50307,7 +50307,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STM32U595ZJ</t>
+          <t>STM32U5A5VJ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -50322,14 +50322,14 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STM32U595ZJ</t>
+          <t>STM32U5A5VJ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -50344,14 +50344,14 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>STM32U595ZJ</t>
+          <t>STM32U5A5VJ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -50366,14 +50366,14 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STM32U595ZJ</t>
+          <t>STM32U5A5VJ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -50388,14 +50388,14 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STM32U595ZJ</t>
+          <t>STM32U5A5VJ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -50410,14 +50410,14 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Table 64. Typical dynamic current consumption of peripherals</t>
+          <t>Table 65. Typical dynamic current consumption of peripherals</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>STM32U595QJ</t>
+          <t>STM32U595ZJ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -50439,7 +50439,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>STM32U595QJ</t>
+          <t>STM32U595ZJ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -50461,7 +50461,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>STM32U595QJ</t>
+          <t>STM32U595ZJ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -50483,7 +50483,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>STM32U595QJ</t>
+          <t>STM32U595ZJ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -50505,7 +50505,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>STM32U595QJ</t>
+          <t>STM32U595ZJ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -50527,7 +50527,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>STM32U595QI</t>
+          <t>STM32U595QJ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -50549,7 +50549,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>STM32U595QI</t>
+          <t>STM32U595QJ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -50571,7 +50571,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>STM32U595QI</t>
+          <t>STM32U595QJ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -50593,7 +50593,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>STM32U595QI</t>
+          <t>STM32U595QJ</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -50615,7 +50615,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>STM32U595QI</t>
+          <t>STM32U595QJ</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -50637,7 +50637,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>STM32U595VI</t>
+          <t>STM32U5A5QJ</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -50652,14 +50652,14 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>STM32U595VI</t>
+          <t>STM32U5A5QJ</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -50674,14 +50674,14 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STM32U595VI</t>
+          <t>STM32U5A5QJ</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -50696,14 +50696,14 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STM32U595VI</t>
+          <t>STM32U5A5QJ</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -50718,14 +50718,14 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STM32U595VI</t>
+          <t>STM32U5A5QJ</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -50740,14 +50740,14 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Table 64. Typical dynamic current consumption of peripherals</t>
+          <t>Table 65. Typical dynamic current consumption of peripherals</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STM32U595RI</t>
+          <t>STM32U595QI</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -50769,7 +50769,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STM32U595RI</t>
+          <t>STM32U595QI</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -50791,7 +50791,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STM32U595RI</t>
+          <t>STM32U595QI</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -50813,7 +50813,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STM32U595RI</t>
+          <t>STM32U595QI</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -50835,7 +50835,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STM32U595RI</t>
+          <t>STM32U595QI</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -50857,7 +50857,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STM32U595VJ</t>
+          <t>STM32U595VI</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -50879,7 +50879,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>STM32U595VJ</t>
+          <t>STM32U595VI</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -50901,7 +50901,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STM32U595VJ</t>
+          <t>STM32U595VI</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -50923,7 +50923,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>STM32U595VJ</t>
+          <t>STM32U595VI</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -50945,7 +50945,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>STM32U595VJ</t>
+          <t>STM32U595VI</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -50967,7 +50967,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>STM32U595AI</t>
+          <t>STM32U595RI</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -50989,7 +50989,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>STM32U595AI</t>
+          <t>STM32U595RI</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -51011,7 +51011,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STM32U595AI</t>
+          <t>STM32U595RI</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -51033,7 +51033,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>STM32U595AI</t>
+          <t>STM32U595RI</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -51055,7 +51055,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>STM32U595AI</t>
+          <t>STM32U595RI</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -51077,7 +51077,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>STM32U595ZI</t>
+          <t>STM32U595VJ</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -51099,7 +51099,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>STM32U595ZI</t>
+          <t>STM32U595VJ</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -51121,7 +51121,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STM32U595ZI</t>
+          <t>STM32U595VJ</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -51143,7 +51143,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STM32U595ZI</t>
+          <t>STM32U595VJ</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -51165,7 +51165,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>STM32U595ZI</t>
+          <t>STM32U595VJ</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -51187,7 +51187,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>STM32U595RJ</t>
+          <t>STM32U5A5ZJ</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -51202,14 +51202,14 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>STM32U595RJ</t>
+          <t>STM32U5A5ZJ</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -51224,14 +51224,14 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>STM32U595RJ</t>
+          <t>STM32U5A5ZJ</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -51246,14 +51246,14 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>STM32U595RJ</t>
+          <t>STM32U5A5ZJ</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -51268,14 +51268,14 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>STM32U595RJ</t>
+          <t>STM32U5A5ZJ</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -51290,14 +51290,14 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Table 64. Typical dynamic current consumption of peripherals</t>
+          <t>Table 65. Typical dynamic current consumption of peripherals</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>STM32U5A5AJ</t>
+          <t>STM32U595AI</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -51312,14 +51312,14 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>STM32U5A5AJ</t>
+          <t>STM32U595AI</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -51334,14 +51334,14 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>STM32U5A5AJ</t>
+          <t>STM32U595AI</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -51356,14 +51356,14 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STM32U5A5AJ</t>
+          <t>STM32U595AI</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -51378,14 +51378,14 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>STM32U5A5AJ</t>
+          <t>STM32U595AI</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -51400,14 +51400,14 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Table 65. Typical dynamic current consumption of peripherals</t>
+          <t>Table 64. Typical dynamic current consumption of peripherals</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>STM32U595AJ</t>
+          <t>STM32U5A5QI</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -51422,14 +51422,14 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STM32U595AJ</t>
+          <t>STM32U5A5QI</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -51444,14 +51444,14 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>STM32U595AJ</t>
+          <t>STM32U5A5QI</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -51466,14 +51466,14 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>STM32U595AJ</t>
+          <t>STM32U5A5QI</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -51488,14 +51488,14 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>STM32U595AJ</t>
+          <t>STM32U5A5QI</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -51510,14 +51510,14 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Table 64. Typical dynamic current consumption of peripherals</t>
+          <t>Table 65. Typical dynamic current consumption of peripherals</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STM32U599NI</t>
+          <t>STM32U595ZI</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -51539,7 +51539,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>STM32U599NI</t>
+          <t>STM32U595ZI</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -51561,7 +51561,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STM32U599NI</t>
+          <t>STM32U595ZI</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -51583,7 +51583,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>STM32U599NI</t>
+          <t>STM32U595ZI</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -51605,7 +51605,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>STM32U599NI</t>
+          <t>STM32U595ZI</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -51627,7 +51627,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>STM32U599VJ</t>
+          <t>STM32U595RJ</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -51649,7 +51649,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>STM32U599VJ</t>
+          <t>STM32U595RJ</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -51671,7 +51671,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>STM32U599VJ</t>
+          <t>STM32U595RJ</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -51693,7 +51693,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>STM32U599VJ</t>
+          <t>STM32U595RJ</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -51715,7 +51715,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>STM32U599VJ</t>
+          <t>STM32U595RJ</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -51737,7 +51737,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>STM32U599ZI</t>
+          <t>STM32U5A5AJ</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -51752,14 +51752,14 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>STM32U599ZI</t>
+          <t>STM32U5A5AJ</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -51774,14 +51774,14 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>STM32U599ZI</t>
+          <t>STM32U5A5AJ</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -51796,14 +51796,14 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>STM32U599ZI</t>
+          <t>STM32U5A5AJ</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -51818,14 +51818,14 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>STM32U599ZI</t>
+          <t>STM32U5A5AJ</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -51840,14 +51840,14 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Table 64. Typical dynamic current consumption of peripherals</t>
+          <t>Table 65. Typical dynamic current consumption of peripherals</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>STM32U599VI</t>
+          <t>STM32U5A5RJ</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -51862,14 +51862,14 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>STM32U599VI</t>
+          <t>STM32U5A5RJ</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -51884,14 +51884,14 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>STM32U599VI</t>
+          <t>STM32U5A5RJ</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -51906,14 +51906,14 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>STM32U599VI</t>
+          <t>STM32U5A5RJ</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -51928,14 +51928,14 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>STM32U599VI</t>
+          <t>STM32U5A5RJ</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -51950,14 +51950,14 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Table 64. Typical dynamic current consumption of peripherals</t>
+          <t>Table 65. Typical dynamic current consumption of peripherals</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>STM32U599NJ</t>
+          <t>STM32U595AJ</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -51979,7 +51979,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>STM32U599NJ</t>
+          <t>STM32U595AJ</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -52001,7 +52001,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>STM32U599NJ</t>
+          <t>STM32U595AJ</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -52023,7 +52023,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>STM32U599NJ</t>
+          <t>STM32U595AJ</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -52045,7 +52045,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>STM32U599NJ</t>
+          <t>STM32U595AJ</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -52067,7 +52067,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>STM32U599BJ</t>
+          <t>STM32U5F9VJ</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -52082,14 +52082,14 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 19. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>STM32U599BJ</t>
+          <t>STM32U5F9VJ</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -52104,14 +52104,14 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 19. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>STM32U599BJ</t>
+          <t>STM32U5F9VJ</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -52133,7 +52133,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>STM32U599BJ</t>
+          <t>STM32U5F9VJ</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -52155,7 +52155,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>STM32U599BJ</t>
+          <t>STM32U5F9VJ</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -52170,14 +52170,14 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Table 64. Typical dynamic current consumption of peripherals</t>
+          <t>Table 72. Typical dynamic current consumption of peripherals</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>STM32U599ZJ</t>
+          <t>STM32U5F9NJ</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -52192,14 +52192,14 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 19. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>STM32U599ZJ</t>
+          <t>STM32U5F9NJ</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -52214,14 +52214,14 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 19. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>STM32U599ZJ</t>
+          <t>STM32U5F9NJ</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -52243,7 +52243,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>STM32U599ZJ</t>
+          <t>STM32U5F9NJ</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -52265,7 +52265,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>STM32U599ZJ</t>
+          <t>STM32U5F9NJ</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -52280,14 +52280,14 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Table 64. Typical dynamic current consumption of peripherals</t>
+          <t>Table 72. Typical dynamic current consumption of peripherals</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>STM32U575RG</t>
+          <t>STM32U5F9BJ</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -52302,14 +52302,14 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 19. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>STM32U575RG</t>
+          <t>STM32U5F9BJ</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -52324,14 +52324,14 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 19. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>STM32U575RG</t>
+          <t>STM32U5F9BJ</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -52353,7 +52353,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>STM32U575RG</t>
+          <t>STM32U5F9BJ</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -52375,12 +52375,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>STM32U585VI</t>
+          <t>STM32U5F9BJ</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -52390,19 +52390,19 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 72. Typical dynamic current consumption of peripherals</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>STM32U585VI</t>
+          <t>STM32U5G9BJ</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -52412,19 +52412,19 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>STM32U585VI</t>
+          <t>STM32U5G9BJ</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -52434,19 +52434,19 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 20. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>STM32U585VI</t>
+          <t>STM32U5G9BJ</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) max</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -52456,19 +52456,19 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>STM32U575RI</t>
+          <t>STM32U5G9BJ</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -52478,19 +52478,19 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>STM32U575RI</t>
+          <t>STM32U5G9BJ</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -52500,19 +52500,19 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 73. Typical dynamic current consumption of peripherals</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>STM32U575RI</t>
+          <t>STM32U5F9ZJ</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -52522,19 +52522,19 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 19. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>STM32U575RI</t>
+          <t>STM32U5F9ZJ</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) max</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -52544,19 +52544,19 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 19. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>STM32U575VG</t>
+          <t>STM32U5F9ZJ</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -52566,19 +52566,19 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>STM32U575VG</t>
+          <t>STM32U5F9ZJ</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -52588,19 +52588,19 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>STM32U575VG</t>
+          <t>STM32U5F9ZJ</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -52610,19 +52610,19 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 72. Typical dynamic current consumption of peripherals</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>STM32U575VG</t>
+          <t>STM32U5G9ZJ</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) max</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -52632,19 +52632,19 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 20. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>STM32U575AG</t>
+          <t>STM32U5G9ZJ</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -52654,19 +52654,19 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>STM32U575AG</t>
+          <t>STM32U5G9ZJ</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -52676,19 +52676,19 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>STM32U575AG</t>
+          <t>STM32U5G9ZJ</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -52698,19 +52698,19 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>STM32U575AG</t>
+          <t>STM32U5G9ZJ</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) max</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -52720,14 +52720,14 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 73. Typical dynamic current consumption of peripherals</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>STM32U575VI</t>
+          <t>STM32U5G9VJ</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -52742,14 +52742,14 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>STM32U575VI</t>
+          <t>STM32U5G9VJ</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -52764,14 +52764,14 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>STM32U575VI</t>
+          <t>STM32U5G9VJ</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -52786,14 +52786,14 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>STM32U575VI</t>
+          <t>STM32U5G9VJ</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -52808,19 +52808,19 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>STM32U575ZG</t>
+          <t>STM32U5G9VJ</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -52830,19 +52830,19 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 73. Typical dynamic current consumption of peripherals</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>STM32U575ZG</t>
+          <t>STM32U5G9NJ</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -52852,19 +52852,19 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>STM32U575ZG</t>
+          <t>STM32U5G9NJ</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -52874,19 +52874,19 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 20. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>STM32U575ZG</t>
+          <t>STM32U5G9NJ</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) max</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -52896,19 +52896,19 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>STM32U575AI</t>
+          <t>STM32U5G9NJ</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -52918,19 +52918,19 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>STM32U575AI</t>
+          <t>STM32U5G9NJ</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -52940,19 +52940,19 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 73. Typical dynamic current consumption of peripherals</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>STM32U575AI</t>
+          <t>STM32U599NI</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -52962,19 +52962,19 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>STM32U575AI</t>
+          <t>STM32U599NI</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) max</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -52984,19 +52984,19 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>STM32U575CG</t>
+          <t>STM32U599NI</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -53006,19 +53006,19 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>STM32U575CG</t>
+          <t>STM32U599NI</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -53028,19 +53028,19 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>STM32U575CG</t>
+          <t>STM32U599NI</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -53050,19 +53050,19 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 64. Typical dynamic current consumption of peripherals</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>STM32U575CG</t>
+          <t>STM32U599VJ</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) max</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -53072,19 +53072,19 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>STM32U575ZI</t>
+          <t>STM32U599VJ</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -53101,12 +53101,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>STM32U575ZI</t>
+          <t>STM32U599VJ</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -53116,19 +53116,19 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>STM32U575ZI</t>
+          <t>STM32U599VJ</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -53138,19 +53138,19 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>STM32U575ZI</t>
+          <t>STM32U599VJ</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) max</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -53160,14 +53160,14 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 64. Typical dynamic current consumption of peripherals</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>STM32U575CI</t>
+          <t>STM32U5A9VJ</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -53182,14 +53182,14 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>STM32U575CI</t>
+          <t>STM32U5A9VJ</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -53204,14 +53204,14 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>STM32U575CI</t>
+          <t>STM32U5A9VJ</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -53226,14 +53226,14 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>STM32U575CI</t>
+          <t>STM32U5A9VJ</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -53248,19 +53248,19 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>STM32U585AI</t>
+          <t>STM32U5A9VJ</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -53270,19 +53270,19 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 65. Typical dynamic current consumption of peripherals</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>STM32U585AI</t>
+          <t>STM32U599ZI</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -53292,19 +53292,19 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>STM32U585AI</t>
+          <t>STM32U599ZI</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -53314,19 +53314,19 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>STM32U585AI</t>
+          <t>STM32U599ZI</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) max</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -53336,19 +53336,19 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>STM32U575OG</t>
+          <t>STM32U599ZI</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -53358,19 +53358,19 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>STM32U575OG</t>
+          <t>STM32U599ZI</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -53380,19 +53380,19 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 64. Typical dynamic current consumption of peripherals</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>STM32U575OG</t>
+          <t>STM32U599VI</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -53402,19 +53402,19 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>STM32U575OG</t>
+          <t>STM32U599VI</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) max</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -53424,19 +53424,19 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>STM32U585CI</t>
+          <t>STM32U599VI</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -53446,19 +53446,19 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>STM32U585CI</t>
+          <t>STM32U599VI</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -53468,19 +53468,19 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>STM32U585CI</t>
+          <t>STM32U599VI</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -53490,19 +53490,19 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 64. Typical dynamic current consumption of peripherals</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>STM32U585CI</t>
+          <t>STM32U5A9NJ</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) max</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -53512,19 +53512,19 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>STM32U585ZI</t>
+          <t>STM32U5A9NJ</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -53541,12 +53541,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>STM32U585ZI</t>
+          <t>STM32U5A9NJ</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -53556,19 +53556,19 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>STM32U585ZI</t>
+          <t>STM32U5A9NJ</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -53578,19 +53578,19 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>STM32U585ZI</t>
+          <t>STM32U5A9NJ</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) max</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -53600,14 +53600,14 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 65. Typical dynamic current consumption of peripherals</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>STM32U575OI</t>
+          <t>STM32U5A9BJ</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -53622,14 +53622,14 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>STM32U575OI</t>
+          <t>STM32U5A9BJ</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -53644,14 +53644,14 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>STM32U575OI</t>
+          <t>STM32U5A9BJ</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -53666,14 +53666,14 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>STM32U575OI</t>
+          <t>STM32U5A9BJ</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -53688,19 +53688,19 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>STM32U585OI</t>
+          <t>STM32U5A9BJ</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -53710,19 +53710,19 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 65. Typical dynamic current consumption of peripherals</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>STM32U585OI</t>
+          <t>STM32U599NJ</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -53732,19 +53732,19 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>STM32U585OI</t>
+          <t>STM32U599NJ</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -53754,19 +53754,19 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>STM32U585OI</t>
+          <t>STM32U599NJ</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) max</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -53776,19 +53776,19 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>STM32U575QG</t>
+          <t>STM32U599NJ</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -53798,19 +53798,19 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>STM32U575QG</t>
+          <t>STM32U599NJ</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -53820,19 +53820,19 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 64. Typical dynamic current consumption of peripherals</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>STM32U575QG</t>
+          <t>STM32U599BJ</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -53842,19 +53842,19 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>STM32U575QG</t>
+          <t>STM32U599BJ</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) max</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -53864,19 +53864,19 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>STM32U585QI</t>
+          <t>STM32U599BJ</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -53886,19 +53886,19 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>STM32U585QI</t>
+          <t>STM32U599BJ</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -53908,19 +53908,19 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>STM32U585QI</t>
+          <t>STM32U599BJ</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -53930,19 +53930,19 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 64. Typical dynamic current consumption of peripherals</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>STM32U585QI</t>
+          <t>STM32U599ZJ</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) max</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -53952,19 +53952,19 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>STM32U585RI</t>
+          <t>STM32U599ZJ</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -53974,19 +53974,19 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>STM32U585RI</t>
+          <t>STM32U599ZJ</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -53996,19 +53996,19 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>STM32U585RI</t>
+          <t>STM32U599ZJ</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -54018,19 +54018,19 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>STM32U585RI</t>
+          <t>STM32U599ZJ</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) max</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -54040,14 +54040,14 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 64. Typical dynamic current consumption of peripherals</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>STM32U575QI</t>
+          <t>STM32U5A9ZJ</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -54062,14 +54062,14 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>STM32U575QI</t>
+          <t>STM32U5A9ZJ</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -54084,14 +54084,14 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>STM32U575QI</t>
+          <t>STM32U5A9ZJ</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -54106,14 +54106,14 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>STM32U575QI</t>
+          <t>STM32U5A9ZJ</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -54128,19 +54128,19 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>STM32U535CE</t>
+          <t>STM32U5A9ZJ</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -54150,19 +54150,19 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 65. Typical dynamic current consumption of peripherals</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>STM32U535CE</t>
+          <t>STM32U575RG</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -54179,12 +54179,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>STM32U535CE</t>
+          <t>STM32U575RG</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -54194,19 +54194,19 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>STM32U535CE</t>
+          <t>STM32U575RG</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) max</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -54216,19 +54216,19 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>STM32U545VE</t>
+          <t>STM32U575RG</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -54238,19 +54238,19 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>STM32U545VE</t>
+          <t>STM32U585VI</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -54267,12 +54267,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>STM32U545VE</t>
+          <t>STM32U585VI</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -54282,19 +54282,19 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>STM32U545VE</t>
+          <t>STM32U585VI</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) max</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -54304,19 +54304,19 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>STM32U535VE</t>
+          <t>STM32U585VI</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -54326,19 +54326,19 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>STM32U535VE</t>
+          <t>STM32U575RI</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -54355,12 +54355,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>STM32U535VE</t>
+          <t>STM32U575RI</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -54370,19 +54370,19 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>STM32U535VE</t>
+          <t>STM32U575RI</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) max</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -54392,19 +54392,19 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>STM32U545RE</t>
+          <t>STM32U575RI</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -54414,19 +54414,19 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>STM32U545RE</t>
+          <t>STM32U575VG</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -54436,19 +54436,19 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>STM32U545RE</t>
+          <t>STM32U575VG</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -54458,19 +54458,19 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>STM32U545RE</t>
+          <t>STM32U575VG</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) max</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -54480,19 +54480,19 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>STM32U535RE</t>
+          <t>STM32U575VG</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -54502,19 +54502,19 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>STM32U535RE</t>
+          <t>STM32U575AG</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -54531,12 +54531,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>STM32U535RE</t>
+          <t>STM32U575AG</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -54546,19 +54546,19 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>STM32U535RE</t>
+          <t>STM32U575AG</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) max</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -54568,19 +54568,19 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>STM32U545CE</t>
+          <t>STM32U575AG</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -54590,19 +54590,19 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>STM32U545CE</t>
+          <t>STM32U575VI</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -54612,19 +54612,19 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>STM32U545CE</t>
+          <t>STM32U575VI</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -54634,19 +54634,19 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>STM32U545CE</t>
+          <t>STM32U575VI</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) max</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -54656,19 +54656,19 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>STM32U535RB</t>
+          <t>STM32U575VI</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -54678,19 +54678,19 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>STM32U535RB</t>
+          <t>STM32U575ZG</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -54707,12 +54707,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>STM32U535RB</t>
+          <t>STM32U575ZG</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -54722,19 +54722,19 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>STM32U535RB</t>
+          <t>STM32U575ZG</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) max</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -54744,19 +54744,19 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>STM32U535CC</t>
+          <t>STM32U575ZG</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -54766,19 +54766,19 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>STM32U535CC</t>
+          <t>STM32U575AI</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -54795,12 +54795,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>STM32U535CC</t>
+          <t>STM32U575AI</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -54810,19 +54810,19 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>STM32U535CC</t>
+          <t>STM32U575AI</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) max</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -54832,19 +54832,19 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>STM32U535CB</t>
+          <t>STM32U575AI</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -54854,19 +54854,19 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>STM32U535CB</t>
+          <t>STM32U575CG</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -54883,12 +54883,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>STM32U535CB</t>
+          <t>STM32U575CG</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -54898,19 +54898,19 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>STM32U535CB</t>
+          <t>STM32U575CG</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) max</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -54920,19 +54920,19 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>STM32U545JE</t>
+          <t>STM32U575CG</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -54942,19 +54942,19 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>STM32U545JE</t>
+          <t>STM32U575ZI</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -54964,19 +54964,19 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>STM32U545JE</t>
+          <t>STM32U575ZI</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -54986,19 +54986,19 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>STM32U545JE</t>
+          <t>STM32U575ZI</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) max</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -55008,19 +55008,19 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>STM32U535RC</t>
+          <t>STM32U575ZI</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -55030,19 +55030,19 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>STM32U535RC</t>
+          <t>STM32U575CI</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -55059,12 +55059,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>STM32U535RC</t>
+          <t>STM32U575CI</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -55074,19 +55074,19 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>STM32U535RC</t>
+          <t>STM32U575CI</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) max</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -55096,19 +55096,19 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>STM32U535JE</t>
+          <t>STM32U575CI</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -55118,19 +55118,19 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>STM32U535JE</t>
+          <t>STM32U585AI</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -55140,19 +55140,19 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>STM32U535JE</t>
+          <t>STM32U585AI</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -55162,19 +55162,19 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>STM32U535JE</t>
+          <t>STM32U585AI</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) max</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -55184,19 +55184,19 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>STM32U535VC</t>
+          <t>STM32U585AI</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -55206,19 +55206,19 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>STM32U535VC</t>
+          <t>STM32U575OG</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -55235,12 +55235,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>STM32U535VC</t>
+          <t>STM32U575OG</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -55250,19 +55250,19 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>STM32U535VC</t>
+          <t>STM32U575OG</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) max</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -55272,19 +55272,19 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>STM32U535NE</t>
+          <t>STM32U575OG</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -55294,19 +55294,19 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>STM32U535NE</t>
+          <t>STM32U585CI</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -55316,19 +55316,19 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>STM32U535NE</t>
+          <t>STM32U585CI</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -55338,19 +55338,19 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>STM32U535NE</t>
+          <t>STM32U585CI</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) max</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -55360,19 +55360,19 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>STM32U545NE</t>
+          <t>STM32U585CI</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -55382,19 +55382,19 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>STM32U545NE</t>
+          <t>STM32U585ZI</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -55411,12 +55411,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>STM32U545NE</t>
+          <t>STM32U585ZI</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -55426,19 +55426,19 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>STM32U545NE</t>
+          <t>STM32U585ZI</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) max</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -55448,19 +55448,19 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>STM32U535NC</t>
+          <t>STM32U585ZI</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -55470,19 +55470,19 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>STM32U535NC</t>
+          <t>STM32U575OI</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -55499,12 +55499,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>STM32U535NC</t>
+          <t>STM32U575OI</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -55514,27 +55514,1897 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
+          <t>STM32U575OI</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>STM32U575OI</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>STM32U585OI</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>STM32U585OI</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>STM32U585OI</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>STM32U585OI</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>STM32U575QG</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>STM32U575QG</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>STM32U575QG</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>STM32U575QG</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>STM32U585QI</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>STM32U585QI</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>STM32U585QI</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>STM32U585QI</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>STM32U585RI</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>STM32U585RI</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>STM32U585RI</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>STM32U585RI</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>STM32U575QI</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>STM32U575QI</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>STM32U575QI</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>STM32U575QI</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>STM32U535CE</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>STM32U535CE</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>STM32U535CE</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>STM32U535CE</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>STM32U545VE</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>STM32U545VE</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>STM32U545VE</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>STM32U545VE</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>STM32U535VE</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>STM32U535VE</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>STM32U535VE</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>STM32U535VE</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>STM32U545RE</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>STM32U545RE</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>STM32U545RE</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>STM32U545RE</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>STM32U535RE</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>STM32U535RE</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>STM32U535RE</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>STM32U535RE</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>STM32U545CE</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>STM32U545CE</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>STM32U545CE</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>STM32U545CE</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>STM32U535RB</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>STM32U535RB</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>STM32U535RB</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>STM32U535RB</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>STM32U535CC</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>STM32U535CC</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>STM32U535CC</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>STM32U535CC</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>STM32U535CB</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>STM32U535CB</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>STM32U535CB</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>STM32U535CB</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>STM32U545JE</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>STM32U545JE</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>STM32U545JE</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>STM32U545JE</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>STM32U535RC</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>STM32U535RC</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>STM32U535RC</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>STM32U535RC</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>STM32U535JE</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>STM32U535JE</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>STM32U535JE</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>STM32U535JE</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>STM32U535VC</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>STM32U535VC</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>STM32U535VC</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>STM32U535VC</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>STM32U535NE</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>STM32U535NE</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>STM32U535NE</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>STM32U535NE</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>STM32U545NE</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>STM32U545NE</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>STM32U545NE</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>STM32U545NE</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
           <t>STM32U535NC</t>
         </is>
       </c>
-      <c r="B249" t="inlineStr">
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>STM32U535NC</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>STM32U535NC</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>STM32U535NC</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
         <is>
           <t>Supply Voltage (V) max</t>
         </is>
       </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr">
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
         <is>
           <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>

--- a/product_selector_out/STM32U5 series.xlsx
+++ b/product_selector_out/STM32U5 series.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM85"/>
+  <dimension ref="A1:BN85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.91796875" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,8 @@
     <col width="21.765625" customWidth="1" min="62" max="62"/>
     <col width="18" customWidth="1" min="63" max="63"/>
     <col width="18" customWidth="1" min="64" max="64"/>
-    <col width="52" customWidth="1" min="65" max="65"/>
+    <col width="18" customWidth="1" min="65" max="65"/>
+    <col width="52" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -895,6 +896,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -990,6 +996,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1314,6 +1321,11 @@
       </c>
       <c r="BM12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u5f7vj.pdf</t>
         </is>
       </c>
@@ -1641,6 +1653,11 @@
       </c>
       <c r="BM13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u5g7vj.pdf</t>
         </is>
       </c>
@@ -1968,6 +1985,11 @@
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u5a5aj.pdf</t>
         </is>
       </c>
@@ -2295,6 +2317,11 @@
       </c>
       <c r="BM15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u595ai.pdf</t>
         </is>
       </c>
@@ -2622,6 +2649,11 @@
       </c>
       <c r="BM16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u595ai.pdf</t>
         </is>
       </c>
@@ -2949,6 +2981,11 @@
       </c>
       <c r="BM17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u5a5aj.pdf</t>
         </is>
       </c>
@@ -3276,6 +3313,11 @@
       </c>
       <c r="BM18" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u595ai.pdf</t>
         </is>
       </c>
@@ -3603,6 +3645,11 @@
       </c>
       <c r="BM19" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u595ai.pdf</t>
         </is>
       </c>
@@ -3930,6 +3977,11 @@
       </c>
       <c r="BM20" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u595ai.pdf</t>
         </is>
       </c>
@@ -4257,6 +4309,11 @@
       </c>
       <c r="BM21" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN21" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u595ai.pdf</t>
         </is>
       </c>
@@ -4584,6 +4641,11 @@
       </c>
       <c r="BM22" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN22" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u5a5aj.pdf</t>
         </is>
       </c>
@@ -4911,6 +4973,11 @@
       </c>
       <c r="BM23" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN23" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u595ai.pdf</t>
         </is>
       </c>
@@ -5238,6 +5305,11 @@
       </c>
       <c r="BM24" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN24" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u5a5aj.pdf</t>
         </is>
       </c>
@@ -5565,6 +5637,11 @@
       </c>
       <c r="BM25" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN25" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u595ai.pdf</t>
         </is>
       </c>
@@ -5892,6 +5969,11 @@
       </c>
       <c r="BM26" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN26" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u595ai.pdf</t>
         </is>
       </c>
@@ -6219,6 +6301,11 @@
       </c>
       <c r="BM27" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN27" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u5a5aj.pdf</t>
         </is>
       </c>
@@ -6546,6 +6633,11 @@
       </c>
       <c r="BM28" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN28" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u5a5aj.pdf</t>
         </is>
       </c>
@@ -6873,6 +6965,11 @@
       </c>
       <c r="BM29" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN29" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u595ai.pdf</t>
         </is>
       </c>
@@ -7200,6 +7297,11 @@
       </c>
       <c r="BM30" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN30" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u5f7vj.pdf</t>
         </is>
       </c>
@@ -7527,6 +7629,11 @@
       </c>
       <c r="BM31" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN31" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u5f7vj.pdf</t>
         </is>
       </c>
@@ -7854,6 +7961,11 @@
       </c>
       <c r="BM32" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN32" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u5f7vj.pdf</t>
         </is>
       </c>
@@ -8181,6 +8293,11 @@
       </c>
       <c r="BM33" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN33" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u5g7vj.pdf</t>
         </is>
       </c>
@@ -8508,6 +8625,11 @@
       </c>
       <c r="BM34" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN34" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u5f7vj.pdf</t>
         </is>
       </c>
@@ -8835,6 +8957,11 @@
       </c>
       <c r="BM35" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN35" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u5g7vj.pdf</t>
         </is>
       </c>
@@ -9162,6 +9289,11 @@
       </c>
       <c r="BM36" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN36" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u5g7vj.pdf</t>
         </is>
       </c>
@@ -9489,6 +9621,11 @@
       </c>
       <c r="BM37" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN37" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u5g7vj.pdf</t>
         </is>
       </c>
@@ -9816,6 +9953,11 @@
       </c>
       <c r="BM38" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN38" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u595ai.pdf</t>
         </is>
       </c>
@@ -10143,6 +10285,11 @@
       </c>
       <c r="BM39" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN39" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u595ai.pdf</t>
         </is>
       </c>
@@ -10470,6 +10617,11 @@
       </c>
       <c r="BM40" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN40" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u5a5aj.pdf</t>
         </is>
       </c>
@@ -10797,6 +10949,11 @@
       </c>
       <c r="BM41" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN41" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u595ai.pdf</t>
         </is>
       </c>
@@ -11124,6 +11281,11 @@
       </c>
       <c r="BM42" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN42" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u595ai.pdf</t>
         </is>
       </c>
@@ -11451,6 +11613,11 @@
       </c>
       <c r="BM43" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN43" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u5a5aj.pdf</t>
         </is>
       </c>
@@ -11778,6 +11945,11 @@
       </c>
       <c r="BM44" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN44" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u5a5aj.pdf</t>
         </is>
       </c>
@@ -12105,6 +12277,11 @@
       </c>
       <c r="BM45" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN45" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u595ai.pdf</t>
         </is>
       </c>
@@ -12432,6 +12609,11 @@
       </c>
       <c r="BM46" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN46" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u595ai.pdf</t>
         </is>
       </c>
@@ -12759,6 +12941,11 @@
       </c>
       <c r="BM47" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN47" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u595ai.pdf</t>
         </is>
       </c>
@@ -13086,6 +13273,11 @@
       </c>
       <c r="BM48" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN48" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u5a5aj.pdf</t>
         </is>
       </c>
@@ -13413,6 +13605,11 @@
       </c>
       <c r="BM49" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN49" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u575ag.pdf</t>
         </is>
       </c>
@@ -13740,6 +13937,11 @@
       </c>
       <c r="BM50" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN50" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u585ai.pdf</t>
         </is>
       </c>
@@ -14067,6 +14269,11 @@
       </c>
       <c r="BM51" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN51" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u575ag.pdf</t>
         </is>
       </c>
@@ -14394,6 +14601,11 @@
       </c>
       <c r="BM52" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN52" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u575ag.pdf</t>
         </is>
       </c>
@@ -14721,6 +14933,11 @@
       </c>
       <c r="BM53" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN53" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u575ag.pdf</t>
         </is>
       </c>
@@ -15048,6 +15265,11 @@
       </c>
       <c r="BM54" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN54" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u575ag.pdf</t>
         </is>
       </c>
@@ -15375,6 +15597,11 @@
       </c>
       <c r="BM55" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN55" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u575ag.pdf</t>
         </is>
       </c>
@@ -15702,6 +15929,11 @@
       </c>
       <c r="BM56" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN56" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u575ag.pdf</t>
         </is>
       </c>
@@ -16029,6 +16261,11 @@
       </c>
       <c r="BM57" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN57" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u575ag.pdf</t>
         </is>
       </c>
@@ -16356,6 +16593,11 @@
       </c>
       <c r="BM58" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN58" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u575ag.pdf</t>
         </is>
       </c>
@@ -16683,6 +16925,11 @@
       </c>
       <c r="BM59" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN59" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u575ag.pdf</t>
         </is>
       </c>
@@ -17010,6 +17257,11 @@
       </c>
       <c r="BM60" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN60" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u585ai.pdf</t>
         </is>
       </c>
@@ -17337,6 +17589,11 @@
       </c>
       <c r="BM61" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN61" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u575ag.pdf</t>
         </is>
       </c>
@@ -17664,6 +17921,11 @@
       </c>
       <c r="BM62" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN62" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u585ai.pdf</t>
         </is>
       </c>
@@ -17991,6 +18253,11 @@
       </c>
       <c r="BM63" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN63" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u585ai.pdf</t>
         </is>
       </c>
@@ -18318,6 +18585,11 @@
       </c>
       <c r="BM64" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN64" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u575ag.pdf</t>
         </is>
       </c>
@@ -18645,6 +18917,11 @@
       </c>
       <c r="BM65" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN65" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u585ai.pdf</t>
         </is>
       </c>
@@ -18972,6 +19249,11 @@
       </c>
       <c r="BM66" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN66" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u575ag.pdf</t>
         </is>
       </c>
@@ -19299,6 +19581,11 @@
       </c>
       <c r="BM67" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN67" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u585ai.pdf</t>
         </is>
       </c>
@@ -19626,6 +19913,11 @@
       </c>
       <c r="BM68" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN68" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u585ai.pdf</t>
         </is>
       </c>
@@ -19953,6 +20245,11 @@
       </c>
       <c r="BM69" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN69" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u575ag.pdf</t>
         </is>
       </c>
@@ -20280,6 +20577,11 @@
       </c>
       <c r="BM70" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN70" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u535cb.pdf</t>
         </is>
       </c>
@@ -20607,6 +20909,11 @@
       </c>
       <c r="BM71" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN71" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u545ce.pdf</t>
         </is>
       </c>
@@ -20934,6 +21241,11 @@
       </c>
       <c r="BM72" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN72" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u535cb.pdf</t>
         </is>
       </c>
@@ -21261,6 +21573,11 @@
       </c>
       <c r="BM73" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN73" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u545ce.pdf</t>
         </is>
       </c>
@@ -21588,6 +21905,11 @@
       </c>
       <c r="BM74" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN74" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u535cb.pdf</t>
         </is>
       </c>
@@ -21915,6 +22237,11 @@
       </c>
       <c r="BM75" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN75" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u545ce.pdf</t>
         </is>
       </c>
@@ -22242,6 +22569,11 @@
       </c>
       <c r="BM76" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN76" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u535cb.pdf</t>
         </is>
       </c>
@@ -22569,6 +22901,11 @@
       </c>
       <c r="BM77" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN77" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u535cb.pdf</t>
         </is>
       </c>
@@ -22896,6 +23233,11 @@
       </c>
       <c r="BM78" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN78" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u535cb.pdf</t>
         </is>
       </c>
@@ -23223,6 +23565,11 @@
       </c>
       <c r="BM79" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN79" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u545ce.pdf</t>
         </is>
       </c>
@@ -23550,6 +23897,11 @@
       </c>
       <c r="BM80" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN80" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u535cb.pdf</t>
         </is>
       </c>
@@ -23877,6 +24229,11 @@
       </c>
       <c r="BM81" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN81" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u535cb.pdf</t>
         </is>
       </c>
@@ -24204,6 +24561,11 @@
       </c>
       <c r="BM82" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN82" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u535cb.pdf</t>
         </is>
       </c>
@@ -24531,6 +24893,11 @@
       </c>
       <c r="BM83" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN83" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u535cb.pdf</t>
         </is>
       </c>
@@ -24858,6 +25225,11 @@
       </c>
       <c r="BM84" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN84" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u545ce.pdf</t>
         </is>
       </c>
@@ -25185,12 +25557,17 @@
       </c>
       <c r="BM85" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN85" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u535cb.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="64">
+  <mergeCells count="65">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -25211,16 +25588,14 @@
     <mergeCell ref="BA10:BA11"/>
     <mergeCell ref="BG10:BG11"/>
     <mergeCell ref="Q10:Q11"/>
-    <mergeCell ref="A1:BM8"/>
     <mergeCell ref="AR10:AR11"/>
+    <mergeCell ref="AT10:AT11"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="BI10:BI11"/>
     <mergeCell ref="AV10:AV11"/>
-    <mergeCell ref="A9:BM9"/>
     <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -25233,6 +25608,7 @@
     <mergeCell ref="AQ10:AQ11"/>
     <mergeCell ref="AW10:AW11"/>
     <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
     <mergeCell ref="BK10:BK11"/>
     <mergeCell ref="A10:A11"/>
@@ -25252,7 +25628,9 @@
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="AG10:AG11"/>
     <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A9:BN9"/>
     <mergeCell ref="H10:H11"/>
+    <mergeCell ref="A1:BN8"/>
     <mergeCell ref="T10:T11"/>
     <mergeCell ref="J10:J11"/>
   </mergeCells>
@@ -25343,7 +25721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM85"/>
+  <dimension ref="A1:BN85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -25411,6 +25789,7 @@
     <col width="16" customWidth="1" min="63" max="63"/>
     <col width="16" customWidth="1" min="64" max="64"/>
     <col width="16" customWidth="1" min="65" max="65"/>
+    <col width="16" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -25744,6 +26123,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -25839,6 +26223,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -26161,7 +26546,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM12" s="6" t="inlineStr">
+      <c r="BM12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -26488,7 +26878,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM13" s="6" t="inlineStr">
+      <c r="BM13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -26815,7 +27210,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM14" s="6" t="inlineStr">
+      <c r="BM14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -27142,7 +27542,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM15" s="6" t="inlineStr">
+      <c r="BM15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -27469,7 +27874,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM16" s="6" t="inlineStr">
+      <c r="BM16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -27796,7 +28206,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM17" s="6" t="inlineStr">
+      <c r="BM17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -28123,7 +28538,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM18" s="6" t="inlineStr">
+      <c r="BM18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -28450,7 +28870,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM19" s="6" t="inlineStr">
+      <c r="BM19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -28777,7 +29202,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM20" s="6" t="inlineStr">
+      <c r="BM20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -29104,7 +29534,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM21" s="6" t="inlineStr">
+      <c r="BM21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN21" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -29431,7 +29866,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM22" s="6" t="inlineStr">
+      <c r="BM22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN22" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -29758,7 +30198,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM23" s="6" t="inlineStr">
+      <c r="BM23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN23" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -30085,7 +30530,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM24" s="6" t="inlineStr">
+      <c r="BM24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN24" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -30412,7 +30862,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM25" s="6" t="inlineStr">
+      <c r="BM25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN25" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -30739,7 +31194,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM26" s="6" t="inlineStr">
+      <c r="BM26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN26" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -31066,7 +31526,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM27" s="6" t="inlineStr">
+      <c r="BM27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN27" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -31393,7 +31858,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM28" s="6" t="inlineStr">
+      <c r="BM28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN28" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -31720,7 +32190,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM29" s="6" t="inlineStr">
+      <c r="BM29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN29" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -32047,7 +32522,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM30" s="6" t="inlineStr">
+      <c r="BM30" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN30" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -32374,7 +32854,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM31" s="6" t="inlineStr">
+      <c r="BM31" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN31" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -32701,7 +33186,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM32" s="6" t="inlineStr">
+      <c r="BM32" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN32" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -33028,7 +33518,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM33" s="6" t="inlineStr">
+      <c r="BM33" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN33" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -33355,7 +33850,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM34" s="6" t="inlineStr">
+      <c r="BM34" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN34" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -33682,7 +34182,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM35" s="6" t="inlineStr">
+      <c r="BM35" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN35" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -34009,7 +34514,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM36" s="6" t="inlineStr">
+      <c r="BM36" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN36" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -34336,7 +34846,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM37" s="6" t="inlineStr">
+      <c r="BM37" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN37" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -34663,7 +35178,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM38" s="6" t="inlineStr">
+      <c r="BM38" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN38" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -34990,7 +35510,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM39" s="6" t="inlineStr">
+      <c r="BM39" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN39" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -35317,7 +35842,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM40" s="6" t="inlineStr">
+      <c r="BM40" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN40" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -35644,7 +36174,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM41" s="6" t="inlineStr">
+      <c r="BM41" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN41" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -35971,7 +36506,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM42" s="6" t="inlineStr">
+      <c r="BM42" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN42" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -36298,7 +36838,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM43" s="6" t="inlineStr">
+      <c r="BM43" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN43" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -36625,7 +37170,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM44" s="6" t="inlineStr">
+      <c r="BM44" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN44" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -36952,7 +37502,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM45" s="6" t="inlineStr">
+      <c r="BM45" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN45" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -37279,7 +37834,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM46" s="6" t="inlineStr">
+      <c r="BM46" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN46" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -37606,7 +38166,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM47" s="6" t="inlineStr">
+      <c r="BM47" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN47" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -37933,7 +38498,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM48" s="6" t="inlineStr">
+      <c r="BM48" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN48" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -38260,7 +38830,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM49" s="6" t="inlineStr">
+      <c r="BM49" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN49" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -38587,7 +39162,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM50" s="6" t="inlineStr">
+      <c r="BM50" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN50" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -38914,7 +39494,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM51" s="6" t="inlineStr">
+      <c r="BM51" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN51" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -39241,7 +39826,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM52" s="6" t="inlineStr">
+      <c r="BM52" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN52" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -39568,7 +40158,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM53" s="6" t="inlineStr">
+      <c r="BM53" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN53" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -39895,7 +40490,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM54" s="6" t="inlineStr">
+      <c r="BM54" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN54" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -40222,7 +40822,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM55" s="6" t="inlineStr">
+      <c r="BM55" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN55" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -40549,7 +41154,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM56" s="6" t="inlineStr">
+      <c r="BM56" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN56" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -40876,7 +41486,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM57" s="6" t="inlineStr">
+      <c r="BM57" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN57" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -41203,7 +41818,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM58" s="6" t="inlineStr">
+      <c r="BM58" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN58" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -41530,7 +42150,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM59" s="6" t="inlineStr">
+      <c r="BM59" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN59" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -41857,7 +42482,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM60" s="6" t="inlineStr">
+      <c r="BM60" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN60" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -42184,7 +42814,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM61" s="6" t="inlineStr">
+      <c r="BM61" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN61" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -42511,7 +43146,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM62" s="6" t="inlineStr">
+      <c r="BM62" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN62" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -42838,7 +43478,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM63" s="6" t="inlineStr">
+      <c r="BM63" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN63" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -43165,7 +43810,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM64" s="6" t="inlineStr">
+      <c r="BM64" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN64" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -43492,7 +44142,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM65" s="6" t="inlineStr">
+      <c r="BM65" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN65" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -43819,7 +44474,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM66" s="6" t="inlineStr">
+      <c r="BM66" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN66" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -44146,7 +44806,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM67" s="6" t="inlineStr">
+      <c r="BM67" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN67" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -44473,7 +45138,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM68" s="6" t="inlineStr">
+      <c r="BM68" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN68" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -44800,7 +45470,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM69" s="6" t="inlineStr">
+      <c r="BM69" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN69" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -45127,7 +45802,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM70" s="6" t="inlineStr">
+      <c r="BM70" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN70" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -45454,7 +46134,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM71" s="6" t="inlineStr">
+      <c r="BM71" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN71" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -45781,7 +46466,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM72" s="6" t="inlineStr">
+      <c r="BM72" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN72" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -46108,7 +46798,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM73" s="6" t="inlineStr">
+      <c r="BM73" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN73" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -46435,7 +47130,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM74" s="6" t="inlineStr">
+      <c r="BM74" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN74" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -46762,7 +47462,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM75" s="6" t="inlineStr">
+      <c r="BM75" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN75" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -47089,7 +47794,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM76" s="6" t="inlineStr">
+      <c r="BM76" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN76" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -47416,7 +48126,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM77" s="6" t="inlineStr">
+      <c r="BM77" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN77" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -47743,7 +48458,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM78" s="6" t="inlineStr">
+      <c r="BM78" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN78" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -48070,7 +48790,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM79" s="6" t="inlineStr">
+      <c r="BM79" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN79" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -48397,7 +49122,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM80" s="6" t="inlineStr">
+      <c r="BM80" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN80" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -48724,7 +49454,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM81" s="6" t="inlineStr">
+      <c r="BM81" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN81" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -49051,7 +49786,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM82" s="6" t="inlineStr">
+      <c r="BM82" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN82" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -49378,7 +50118,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM83" s="6" t="inlineStr">
+      <c r="BM83" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN83" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -49705,7 +50450,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM84" s="6" t="inlineStr">
+      <c r="BM84" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN84" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -50032,7 +50782,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM85" s="6" t="inlineStr">
+      <c r="BM85" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN85" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -50040,8 +50795,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BM9"/>
-    <mergeCell ref="A1:BM8"/>
+    <mergeCell ref="A9:BN9"/>
+    <mergeCell ref="A1:BN8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
